--- a/data/trans_bre/P2A_enfcro_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,45; 16,92</t>
+          <t>9,23; 16,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,8; 13,62</t>
+          <t>6,78; 13,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,42; 18,63</t>
+          <t>10,28; 18,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,46; 14,57</t>
+          <t>4,96; 15,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,46; 28,23</t>
+          <t>14,27; 27,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,8; 18,73</t>
+          <t>8,63; 18,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,39; 28,23</t>
+          <t>14,26; 27,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,54; 28,6</t>
+          <t>8,56; 30,01</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,72; 18,72</t>
+          <t>11,85; 18,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,38; 16,3</t>
+          <t>9,01; 15,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,48; 11,89</t>
+          <t>5,4; 11,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 30,64</t>
+          <t>2,57; 27,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,44; 55,72</t>
+          <t>31,46; 56,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,34; 37,99</t>
+          <t>19,64; 36,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,82; 27,38</t>
+          <t>11,56; 27,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 126,47</t>
+          <t>7,62; 117,49</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,54; 18,67</t>
+          <t>6,29; 18,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 13,15</t>
+          <t>-0,41; 13,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 13,69</t>
+          <t>2,1; 14,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 6,86</t>
+          <t>-3,24; 6,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,07; 55,47</t>
+          <t>15,37; 55,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 31,4</t>
+          <t>-0,82; 33,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,07; 38,88</t>
+          <t>5,07; 41,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 26,84</t>
+          <t>-10,56; 25,17</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,69; 18,43</t>
+          <t>13,69; 18,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,63; 16,24</t>
+          <t>11,41; 16,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,39; 14,09</t>
+          <t>9,21; 14,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,12; 23,73</t>
+          <t>5,04; 23,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,96; 42,9</t>
+          <t>29,99; 43,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,1; 31,03</t>
+          <t>20,74; 30,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,63; 29,1</t>
+          <t>17,88; 29,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,56; 85,41</t>
+          <t>14,31; 85,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_enfcro_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,1</t>
+          <t>12,61</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,23; 16,72</t>
+          <t>9,31; 17,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,78; 13,44</t>
+          <t>7,07; 13,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 18,48</t>
+          <t>10,67; 18,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,96; 15,03</t>
+          <t>7,84; 17,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,27; 27,71</t>
+          <t>14,44; 28,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,63; 18,27</t>
+          <t>9,15; 18,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,26; 27,85</t>
+          <t>14,92; 28,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,56; 30,01</t>
+          <t>14,49; 36,95</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,17</t>
+          <t>3,95</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,85; 18,99</t>
+          <t>11,76; 18,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,01; 15,85</t>
+          <t>9,44; 15,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 11,87</t>
+          <t>5,24; 11,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 27,62</t>
+          <t>1,14; 6,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,46; 56,85</t>
+          <t>31,91; 55,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,64; 36,56</t>
+          <t>20,4; 36,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,56; 27,22</t>
+          <t>10,73; 26,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 117,49</t>
+          <t>3,59; 23,53</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,02</t>
+          <t>2,58</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,29; 18,75</t>
+          <t>5,83; 18,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 13,68</t>
+          <t>-1,21; 13,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 14,51</t>
+          <t>1,58; 13,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 6,55</t>
+          <t>-2,31; 7,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,37; 55,37</t>
+          <t>14,56; 54,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 33,03</t>
+          <t>-1,75; 31,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,07; 41,1</t>
+          <t>3,77; 37,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 25,17</t>
+          <t>-7,3; 29,19</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,77</t>
+          <t>6,73</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,69; 18,36</t>
+          <t>13,65; 18,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,41; 16,06</t>
+          <t>11,32; 16,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,21; 14,27</t>
+          <t>9,09; 14,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,04; 23,6</t>
+          <t>4,63; 9,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,99; 43,08</t>
+          <t>29,81; 42,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,74; 30,74</t>
+          <t>20,41; 30,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,88; 29,55</t>
+          <t>18,01; 29,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,31; 85,63</t>
+          <t>13,21; 28,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_enfcro_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Población que convive con personas con enfermedades crónicas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
